--- a/inst/extdata/misa_data/misa_scenarios.xlsx
+++ b/inst/extdata/misa_data/misa_scenarios.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20408"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20411"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mzamzo\Documents\R\git\kwb.misa\inst\extdata\misa_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pschue\Documents\R\git\kwb.misa\inst\extdata\misa_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02CDAD51-B91F-4464-841F-4EF314E08078}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97AFF7BD-EAF8-4409-9E93-C1ACD69BECF0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -154,9 +154,6 @@
     <t>strlieg_ges_30_mn</t>
   </si>
   <si>
-    <t>Str. + Lieg.30a MN</t>
-  </si>
-  <si>
     <t>9_MN</t>
   </si>
   <si>
@@ -190,28 +187,31 @@
     <t>Str. + Lieg. &gt;30a CF</t>
   </si>
   <si>
-    <t>Straßen 10a MN</t>
-  </si>
-  <si>
-    <t>Liegen. 10a MN</t>
-  </si>
-  <si>
-    <t>Straßen 30a MN</t>
-  </si>
-  <si>
-    <t>Liegen. 30a MN</t>
-  </si>
-  <si>
-    <t>Str. + Lieg. 10a MN</t>
-  </si>
-  <si>
-    <t>Str. + Lieg. &gt;30a MN</t>
-  </si>
-  <si>
     <t>plot_name</t>
   </si>
   <si>
     <t xml:space="preserve">misa_sccenario_no </t>
+  </si>
+  <si>
+    <t>Straßen 10a</t>
+  </si>
+  <si>
+    <t>Liegen. 10a</t>
+  </si>
+  <si>
+    <t>Straßen 30a</t>
+  </si>
+  <si>
+    <t>Liegen. 30a</t>
+  </si>
+  <si>
+    <t>Str. + Lieg. 10a</t>
+  </si>
+  <si>
+    <t>Str. + Lieg.30a</t>
+  </si>
+  <si>
+    <t>Str. + Lieg. &gt;30a</t>
   </si>
 </sst>
 </file>
@@ -1066,7 +1066,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1084,7 +1084,7 @@
         <v>4</v>
       </c>
       <c r="G1" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1104,7 +1104,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1124,7 +1124,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1144,7 +1144,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1167,7 +1167,7 @@
         <v>1.5</v>
       </c>
       <c r="G5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1190,7 +1190,7 @@
         <v>4</v>
       </c>
       <c r="G6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1213,7 +1213,7 @@
         <v>4.5</v>
       </c>
       <c r="G7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1236,7 +1236,7 @@
         <v>22.5</v>
       </c>
       <c r="G8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1259,7 +1259,7 @@
         <v>5.5</v>
       </c>
       <c r="G9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1305,7 +1305,7 @@
         <v>47.5</v>
       </c>
       <c r="G11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1328,7 +1328,7 @@
         <v>4</v>
       </c>
       <c r="G12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1351,7 +1351,7 @@
         <v>6.5</v>
       </c>
       <c r="G13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1374,7 +1374,7 @@
         <v>9</v>
       </c>
       <c r="G14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1397,7 +1397,7 @@
         <v>23.5</v>
       </c>
       <c r="G15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1420,7 +1420,7 @@
         <v>10.5</v>
       </c>
       <c r="G16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1443,12 +1443,12 @@
         <v>32.5</v>
       </c>
       <c r="G17" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B18" t="s">
         <v>28</v>
@@ -1457,7 +1457,7 @@
         <v>29</v>
       </c>
       <c r="D18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E18" t="s">
         <v>33</v>
@@ -1466,7 +1466,7 @@
         <v>50.5</v>
       </c>
       <c r="G18" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/misa_data/misa_scenarios.xlsx
+++ b/inst/extdata/misa_data/misa_scenarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pschue\Documents\R\git\kwb.misa\inst\extdata\misa_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97AFF7BD-EAF8-4409-9E93-C1ACD69BECF0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C90754B5-4D12-4554-9691-983EC0FF2F0B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -193,25 +193,25 @@
     <t xml:space="preserve">misa_sccenario_no </t>
   </si>
   <si>
-    <t>Straßen 10a</t>
-  </si>
-  <si>
-    <t>Liegen. 10a</t>
-  </si>
-  <si>
-    <t>Straßen 30a</t>
-  </si>
-  <si>
-    <t>Liegen. 30a</t>
-  </si>
-  <si>
-    <t>Str. + Lieg. 10a</t>
-  </si>
-  <si>
-    <t>Str. + Lieg.30a</t>
-  </si>
-  <si>
-    <t>Str. + Lieg. &gt;30a</t>
+    <t>Str10a</t>
+  </si>
+  <si>
+    <t>Lieg10a</t>
+  </si>
+  <si>
+    <t>Str30a</t>
+  </si>
+  <si>
+    <t>Lieg30a</t>
+  </si>
+  <si>
+    <t>StrLieg10a</t>
+  </si>
+  <si>
+    <t>StrLieg30a</t>
+  </si>
+  <si>
+    <t>StrLieg&gt;30a</t>
   </si>
 </sst>
 </file>
